--- a/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/liquidity_forecasting.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/liquidity_forecasting.xlsx
@@ -478,14 +478,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>343.8</v>
+        <v>324.9</v>
       </c>
       <c r="C3" t="n">
-        <v>76.59999999999999</v>
+        <v>-18.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>73.4%</t>
         </is>
       </c>
     </row>
@@ -496,14 +496,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>412.5</v>
+        <v>339.5</v>
       </c>
       <c r="C4" t="n">
-        <v>57.4</v>
+        <v>-22</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -514,14 +514,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>313.4</v>
+        <v>309.7</v>
       </c>
       <c r="C5" t="n">
-        <v>-8.5</v>
+        <v>-22</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>88.7%</t>
         </is>
       </c>
     </row>
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>477.1</v>
+        <v>414.4</v>
       </c>
       <c r="C6" t="n">
-        <v>-37.9</v>
+        <v>4.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>95.4%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>401.4</v>
+        <v>496.9</v>
       </c>
       <c r="C7" t="n">
-        <v>-48.9</v>
+        <v>52</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>71.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>391.7</v>
+        <v>439.3</v>
       </c>
       <c r="C8" t="n">
-        <v>16.4</v>
+        <v>35.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>88.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>468.6</v>
+        <v>329.6</v>
       </c>
       <c r="C9" t="n">
-        <v>-16.4</v>
+        <v>-36.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>75.1%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>505.6</v>
+        <v>355.5</v>
       </c>
       <c r="C10" t="n">
-        <v>16.5</v>
+        <v>-17.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>71.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>482.6</v>
+        <v>436.7</v>
       </c>
       <c r="C11" t="n">
-        <v>-28.3</v>
+        <v>-38.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>71.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>543.5</v>
+        <v>378.6</v>
       </c>
       <c r="C12" t="n">
-        <v>-16.6</v>
+        <v>7.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>92.2%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>406.8</v>
+        <v>322.8</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.7%</t>
         </is>
       </c>
     </row>
@@ -676,14 +676,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>534.4</v>
+        <v>449.2</v>
       </c>
       <c r="C14" t="n">
-        <v>77.59999999999999</v>
+        <v>-22.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>341.6</v>
+        <v>458.2</v>
       </c>
       <c r="C15" t="n">
-        <v>9.699999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>94.5%</t>
         </is>
       </c>
     </row>
